--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-organization.xlsx
@@ -903,7 +903,7 @@
 この要素は修飾子としてラベル付けされています。これは、リソースが誤って作成されたことを示すために使用できるためです。</t>
   </si>
   <si>
-    <t>レコードが使用されなくなったことを示すためのフラグが必要で、一般的にUIではユーザのために非表示にする必要がある。</t>
+    <t>レコードが使用されなくなったことを示すためのフラグが必要で、一般的にUIではユーザーのために非表示にする必要がある。</t>
   </si>
   <si>
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
